--- a/04_DESIGN_TABLES/DesignTable_6802.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6802.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AD62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -625,6 +625,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -976,7 +981,7 @@
         <v>0.77</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0.17</v>
@@ -1009,10 +1014,14 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51528 corroborates matched-dash)</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr"/>
+          <t>[BRENNAN-CELL 2026-10-20: HEXB@HEX] JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51528 corroborates matched-dash); HEXB@HEX: Brennan TFA catalog p.41 table TFA-p041-t02 "MJ-MAORB 45 DEG ELBOW" row 6802-04-06-NWO-FG col "C HEX" = 0.688 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 0.56: a 0.56 locknut cannot fit the -06 ORB thread 9/16-18 (major 0.5625); generator BLOCKED ("Air-Way locknut hex 0.56 differs from the Brennan nut 0.6875 for -06"; the Brennan -06 locknut measured on the 6801 STEPs is 0.6875, catalog prints 0.688))</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 HEXB@HEX = Brennan 0.688 (Air-Way 0.56 cannot be built: a 0.56 locknut cannot fit the -06 ORB thread 9/16-18 (major 0.5625); generator BLOCKED ("Air-Way locknut hex 0.56 differs from the Brennan nut 0.6875 for -06"; the Brennan -06 locknut measured on the 6801 STEPs is 0.6875, catalog prints 0.688))</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1021,6 +1030,11 @@
       <c r="AC6" t="inlineStr">
         <is>
           <t>6802-04-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
